--- a/outputs/EMS upgrade output - helideck_safety_equipment.xlsx
+++ b/outputs/EMS upgrade output - helideck_safety_equipment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box structural integrity lost from rust, may collapse or allow water ingress </t>
+          <t xml:space="preserve">Cabinet wall corroded through; water ingress damages stored equipment </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storage box structural condition inspection completed? [Y/N]; Corrosion protection coating intact and effective? [Y/N] </t>
+          <t xml:space="preserve">Cabinet body is free of perforations from corrosion? [Y/N] </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -516,29 +516,29 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.6 - Fatigue </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hinge/mounting bracket fatigue cracking from repeated opening/closing </t>
+          <t xml:space="preserve">Cabinet hinge bracket cracked due to cyclic loading; door may detach </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storage box hinge and bracket condition checked for cracks? [Y/N]; Crack detection performed on mounting points? [Y/N] </t>
+          <t xml:space="preserve">Cabinet hinges and mounting brackets are free of cracks? [Y/N] </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,49 +568,49 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion perforation of box wall allows water ingress to stored equipment </t>
+          <t xml:space="preserve">Cabinet door bent by impact; will not close or seal properly </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storage box interior checked for moisture ingress? [Y/N]; Drain holes open and functional? [Y/N] </t>
+          <t xml:space="preserve">Cabinet door closes flush against the frame without forcing? [Y/N] </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -620,49 +620,49 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Door gasket/seal worn, allows water penetration </t>
+          <t xml:space="preserve">Cabinet door hinge pin broken; door detached </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Door seal condition checked and replaced if worn? [Y/N]; Seal integrity verified? [Y/N] </t>
+          <t xml:space="preserve">Cabinet door hinge pins are intact and securely in place? [Y/N] </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,49 +672,49 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">1.6 - Sticking </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Door hinge or latch seized due to corrosion, preventing immediate access </t>
+          <t xml:space="preserve">Cabinet latch mechanism jammed by corrosion; door cannot be opened </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storage box door opens freely and closes securely? [Y/N]; Hinge and latch mechanism lubricated and free? [Y/N] </t>
+          <t xml:space="preserve">Cabinet latch mechanism operates freely and releases on first attempt? [Y/N] </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,49 +724,49 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.5 - Looseness </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Door latch loose, box may open unintentionally and spill contents </t>
+          <t xml:space="preserve">Door hinges loose; door sags and binds against frame preventing opening </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Door latch secure and properly aligned? [Y/N] </t>
+          <t xml:space="preserve">Cabinet door hinges are tight with no vertical play? [Y/N] </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -783,42 +783,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged / choked </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salt residue or debris buildup inside box restricts drainage </t>
+          <t xml:space="preserve">Door frame bent; door cannot clear the frame to open </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box interior cleaned and free of salt residue or debris? [Y/N] </t>
+          <t xml:space="preserve">Cabinet door frame is square and free of deformation? [Y/N] </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -835,42 +835,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged / choked </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box bottom deformed causing standing water to accumulate </t>
+          <t xml:space="preserve">Corroded hinge pin seized; door will not pivot </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box interior free of standing water? [Y/N] </t>
+          <t xml:space="preserve">Door hinge pins are lubricated and the door swings freely? [Y/N] </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -887,42 +887,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.4 - Wear </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on hinges increases operating force </t>
+          <t xml:space="preserve">Door gasket worn; allows water ingress during rain or sea spray </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hinge condition and operational force within spec? [Y/N] </t>
+          <t xml:space="preserve">Door gasket compresses evenly around the door perimeter when closed? [Y/N] </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -939,42 +939,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box door deformed from impact, no longer seals properly </t>
+          <t xml:space="preserve">Gasket hardened and cracked from UV exposure; no longer seals </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box door free of deformation? [Y/N]; Box alignment checked? [Y/N] </t>
+          <t xml:space="preserve">Door gasket is pliable and free from cracking or hardening? [Y/N] </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -984,49 +984,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">3.4 - Out of adjustment </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hinge fatigue fracture causing door to detach </t>
+          <t xml:space="preserve">Door striker misaligned; gasket not fully compressed </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Door hinge condition checked and free of fatigue cracks? [Y/N] </t>
+          <t xml:space="preserve">Door closes with even resistance without requiring excessive force to latch? [Y/N] </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1036,49 +1036,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mounting bracket fracture from overload </t>
+          <t xml:space="preserve">Gasket retaining channel corroded; gasket displaced creating a leak path </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mounting bracket condition checked and fasteners tight? [Y/N] </t>
+          <t xml:space="preserve">Gasket is fully seated in its channel at all contact points? [Y/N] </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1095,42 +1095,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose hinge or latch produces rattling noise </t>
+          <t xml:space="preserve">Surface rust on cabinet exterior; cosmetic degradation </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box fixings and fasteners checked for tightness? [Y/N] </t>
+          <t xml:space="preserve">Cabinet exterior is free from active rust or corrosion? [Y/N] </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1147,42 +1147,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Helideck Crash Rescue Storage Box Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and protect portable crash rescue equipment from environmental damage </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.5 - Looseness </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn hinge pin or bushing causes metal-on-metal noise </t>
+          <t xml:space="preserve">Cabinet mounting bolts loose; cabinet unstable </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storage box hinge pin and bushing condition inspected? [Y/N] </t>
+          <t xml:space="preserve">All cabinet mounting bolts are torqued to specification? [Y/N] </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1192,49 +1192,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.3 - Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder wall corrosion reduces structural strength </t>
+          <t xml:space="preserve">Paint chipped or peeling; bare metal exposed </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher cylinder body free of corrosion damage? [Y/N]; Extinguisher hydrostatic test within date? [Y/N] </t>
+          <t xml:space="preserve">Cabinet paint coating is intact with no bare metal exposed? [Y/N] </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1244,49 +1244,49 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">6.3 - Other </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure gauge reading incorrect </t>
+          <t xml:space="preserve">Cabinet interior has debris or foreign materials </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher pressure gauge needle within green zone? [Y/N] </t>
+          <t xml:space="preserve">Cabinet interior is clean and free from foreign debris? [Y/N] </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1296,49 +1296,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">PDE - Parameter deviation (*) </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">5.2 - Contamination </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle or pickup tube partially blocked reduces flow </t>
+          <t xml:space="preserve">Internal cabinet humidity too high due to poor ventilation; damages equipment </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher nozzle clear and unobstructed? [Y/N] </t>
+          <t xml:space="preserve">Cabinet interior is dry with no visible condensation or moisture? [Y/N] </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1348,49 +1348,49 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">PDE - Parameter deviation (*) </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">5.1 - Blockage/plugged </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguishing agent contaminated with moisture, causing pressure drop </t>
+          <t xml:space="preserve">Cabinet drain holes (if fitted) blocked; water accumulates inside </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher weight within acceptable range? [Y/N]; Extinguisher last inspection date verified? [Y/N] </t>
+          <t xml:space="preserve">Cabinet drain holes are clear and unobstructed? [Y/N] </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1400,49 +1400,49 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge valve or operating lever seized from corrosion </t>
+          <t xml:space="preserve">Cabinet door completely detached from hinges </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher operating lever moves freely? [Y/N]; Safety pin intact and removable? [Y/N] </t>
+          <t xml:space="preserve">Cabinet door hinge welds and pins are intact and secure? [Y/N] </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1452,49 +1452,49 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Crash Rescue Cabinet Failure *</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Securely house and protect portable crash rescue equipment from the marine environment </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.6 - Sticking </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operating lever loose/worn, mechanism does not engage valve </t>
+          <t xml:space="preserve">Latch mechanism internal spring broken; latch will not retain door closed </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher operating lever condition checked? [Y/N] </t>
+          <t xml:space="preserve">Cabinet latch mechanism holds the door securely closed? [Y/N] </t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1504,49 +1504,49 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder or valve fractured due to impact </t>
+          <t xml:space="preserve">Lanyard snapped due to material fatigue; equipment becomes loose </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher cylinder inspected for dents, bulges, or damage? [Y/N] </t>
+          <t xml:space="preserve">Lanyards and securing straps are intact with no fraying, cuts, or breaks? [Y/N] </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1556,49 +1556,49 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.4 - Wear </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder body deformed from impact </t>
+          <t xml:space="preserve">Lanyard abraded at contacting edges; weakened </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher body free from deformation? [Y/N] </t>
+          <t xml:space="preserve">Lanyards show no signs of abrasion wear at contact points? [Y/N] </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1608,49 +1608,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat distorts valve components causing loss of seal </t>
+          <t xml:space="preserve">Metal buckle or D-ring corroded; structurally compromised </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve and cylinder inspected for heat damage? [Y/N] </t>
+          <t xml:space="preserve">Metal buckles, D-rings, and clips are free from pitting corrosion? [Y/N] </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1660,49 +1660,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">5.3 - Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direct sun exposure causes internal pressure rise </t>
+          <t xml:space="preserve">Lanyard cut by sharp edge inside cabinet; broken </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher stored away from direct sunlight? [Y/N]; Ambient temperature in storage area within safe range? [Y/N] </t>
+          <t xml:space="preserve">All interior surfaces of the cabinet are free from sharp edges? [Y/N] </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1719,42 +1719,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">1.6 - Sticking </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure gauge stuck or giving false reading </t>
+          <t xml:space="preserve">Quick-release buckle seized; cannot be released in an emergency </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extinguisher gauge reading verified and functional? [Y/N] </t>
+          <t xml:space="preserve">Quick-release mechanisms operate smoothly and release instantly? [Y/N] </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1764,49 +1764,49 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portable Fire Extinguisher Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate handheld fire extinguishing capability for small fires </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 No power/voltage </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic status indicator (if fitted) has no power </t>
+          <t xml:space="preserve">Hook or clip corroded and jammed; cannot be released from equipment eyelet </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic status indicator (if fitted) functional? [Y/N] </t>
+          <t xml:space="preserve">All hooks and clips open and close freely without binding? [Y/N] </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1816,49 +1816,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axe head pivot or folding mechanism seized </t>
+          <t xml:space="preserve">Hook bent out of shape; will not engage equipment eyelet properly </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axe head pivot (if folding) moves freely? [Y/N]; Crash axe head tight on handle? [Y/N] </t>
+          <t xml:space="preserve">Retaining hooks are not bent or deformed and engage correctly? [Y/N] </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1868,49 +1868,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">6.3 - Other </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on axe head reduces striking efficiency </t>
+          <t xml:space="preserve">Lanyard tangled around other equipment; cannot be released </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crash axe head free of significant corrosion? [Y/N] </t>
+          <t xml:space="preserve">Lanyards are routed correctly and not tangled with other items? [Y/N] </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1927,42 +1927,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">5.2 - Contamination </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axe head bent from misuse reduces effectiveness </t>
+          <t xml:space="preserve">Lanyard contaminated with oil or grease; slippery to handle </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crash axe head shape correct and functional? [Y/N] </t>
+          <t xml:space="preserve">Lanyards and straps are clean and free from oil, grease, or other contaminants? [Y/N] </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1979,42 +1979,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">6.3 - Other </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handle cracked or broken from impact </t>
+          <t xml:space="preserve">Lanyard not correctly routed; equipment not properly secured </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crash axe handle free of cracks or splits? [Y/N] </t>
+          <t xml:space="preserve">Each rescue item is correctly secured by its designated lanyard? [Y/N] </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2024,49 +2024,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.5 - Looseness </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blade edge blunt or rounded </t>
+          <t xml:space="preserve">Lanyard anchor point in cabinet is loose or detached </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crash axe blade edge sharp enough? [Y/N] </t>
+          <t xml:space="preserve">Lanyard anchor points inside the cabinet are securely fastened? [Y/N] </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2076,49 +2076,49 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.4 - Wear </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pitting corrosion on blade reduces cutting edge </t>
+          <t xml:space="preserve">Lanyard shows discoloration or UV degradation; weakened </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crash axe stored in dry condition? [Y/N]; Axe head protected from corrosion? [Y/N] </t>
+          <t xml:space="preserve">Lanyards are free from UV degradation or discoloration? [Y/N] </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2128,49 +2128,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.5 - Looseness </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handle fatigue fractures during striking </t>
+          <t xml:space="preserve">Lanyard mounting bracket inside cabinet loose; bracket may detach </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axe handle inspected for fatigue cracks? [Y/N] </t>
+          <t xml:space="preserve">Lanyard mounting brackets are securely attached to the cabinet wall? [Y/N] </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2180,49 +2180,49 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head separates from handle during use </t>
+          <t xml:space="preserve">Lanyard anchor bracket corroded; structurally weakened </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axe head fixings tight and secure? [Y/N] </t>
+          <t xml:space="preserve">Lanyard anchor brackets are free from severe corrosion and are structurally sound? [Y/N] </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2232,49 +2232,49 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">PDE - Parameter deviation (*) </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">3.4 - Out of adjustment </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blade chips or breaks during impact </t>
+          <t xml:space="preserve">Lanyard length incorrect; equipment not held snugly against cabinet wall </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blade condition checked for chips or fractures? [Y/N] </t>
+          <t xml:space="preserve">Lanyards are correctly tensioned to hold equipment snugly? [Y/N] </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2291,42 +2291,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Rescue Equipment Lanyard/Strap Failure *</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Secure portable rescue equipment inside the cabinet to prevent movement during vessel motion </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation (*) </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">6.3 - Other </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose axe head makes rattling noise </t>
+          <t xml:space="preserve">Wrong type of lanyard used for the equipment; does not secure it properly </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axe head fixings checked for tightness [Y/N] </t>
+          <t xml:space="preserve">Lanyard type matches the equipment it is securing? [Y/N] </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2343,42 +2343,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Crash Axe Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide forcible entry and rescue tool for helicopter structure </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn handle-to-head interface creates noise </t>
+          <t xml:space="preserve">Label plate bent or warped; text distorted and unreadable </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Axe head/handle interface condition inspected [Y/N] </t>
+          <t xml:space="preserve">Cabinet label is flat and legible without deformation? [Y/N] </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2395,42 +2395,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saw pivot or blade guard jammed due to corrosion </t>
+          <t xml:space="preserve">Label mounting screws corroded; label detached and missing </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue saw mechanism moves freely? [Y/N]; Pivot points lubricated? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label is present and securely attached without signs of severe corrosion? [Y/N] </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2440,49 +2440,49 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on blade or handle weakens cutter </t>
+          <t xml:space="preserve">Label material cracked from UV exposure or impact; pieces missing </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue saw blade condition inspected for corrosion? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label is intact without cracks or missing pieces? [Y/N] </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2499,42 +2499,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">1.5 - Looseness </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blade breaks during cutting due to fatigue </t>
+          <t xml:space="preserve">Label loose on its mounting; rattles in the wind </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue saw blade inspected for cracks or chips? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label is securely attached with no looseness? [Y/N] </t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2544,49 +2544,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blade material fatigue causes fracture during cutting </t>
+          <t xml:space="preserve">Label faded or discolored from UV/salt spray; text difficult to read </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue saw overall condition inspected for fatigue? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label text is clearly readable from a distance of 2 meters? [Y/N] </t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2603,42 +2603,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">5.2 - Contamination </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blade teeth/edge worn, cutting speed reduced </t>
+          <t xml:space="preserve">Label surface covered with dirt, salt, or marine growth; obscuring text </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue saw tooth sharpness adequate? [Y/N]; Cutting edge condition acceptable? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label surface is clean and free from dirt or marine growth? [Y/N] </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2648,49 +2648,49 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">4.2 - Open circuit </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on joints increases friction </t>
+          <t xml:space="preserve">Illuminated label (if fitted) non-functional; not visible at night </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue saw mechanism operates without excess friction? [Y/N] </t>
+          <t xml:space="preserve">Illuminated label (if fitted) illuminates correctly and evenly? [Y/N] </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2700,49 +2700,49 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">6.3 - Other </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handle or guard cracked from impact </t>
+          <t xml:space="preserve">Label text does not match current cabinet contents; outdated </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue saw handle and guard free of cracks? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label matches the current inventory stowed inside? [Y/N] </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2759,42 +2759,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation (*) </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">6.3 - Other </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blade bent from misuse </t>
+          <t xml:space="preserve">Label specifies wrong item class code; does not indicate "Helideck Rescue" </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue saw blade straightness verified? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label correctly indicates "Helideck Crash Rescue Equipment"? [Y/N] </t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2811,42 +2811,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation (*) </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">3.4 - Out of adjustment </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose blade fasteners cause rattling noise </t>
+          <t xml:space="preserve">Label is on the wrong cabinet; swapped with another cabinet's label </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blade fasteners checked for tightness? [Y/N] </t>
+          <t xml:space="preserve">Label corresponds to the correct cabinet location per helideck layout? [Y/N] </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2863,42 +2863,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Emergency Rescue Saw Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide rapid cutting capability to access trapped persons </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn pivot bushing creates grinding noise </t>
+          <t xml:space="preserve">Label completely broken off; no identification present </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pivot bushing condition inspected for wear? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label is physically present and intact? [Y/N] </t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2908,49 +2908,49 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinet Identification/Label Failure *</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Clearly identify cabinet contents and location for rapid identification during emergency </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">5.3 - Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frame or handle cracked from overload </t>
+          <t xml:space="preserve">Label removed by impact or vandals; missing </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher frame and handles inspected for cracks? [Y/N] </t>
+          <t xml:space="preserve">Cabinet label is present and has not been removed or defaced? [Y/N] </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2960,49 +2960,49 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.4 - Wear </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on metal frame reduces load capacity </t>
+          <t xml:space="preserve">Door gasket abraded at contact surface; gap allows water ingress </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher metal components free of significant corrosion? [Y/N] </t>
+          <t xml:space="preserve">Door gasket compresses evenly and fully around the perimeter when closed? [Y/N] </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3012,49 +3012,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Folding/extension mechanism jammed </t>
+          <t xml:space="preserve">Gasket material hardened and cracked from UV/Ozone exposure; seal broken </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher folding mechanism operates freely? [Y/N]; Extension locks engage properly? [Y/N] </t>
+          <t xml:space="preserve">Door gasket is pliable and free from cracking or hardening? [Y/N] </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3064,49 +3064,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">3.4 - Out of adjustment </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Restraint straps frayed or buckles worn </t>
+          <t xml:space="preserve">Door striker misaligned; gasket not fully compressed at all points </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher restraints and buckle condition checked? [Y/N] </t>
+          <t xml:space="preserve">Door closes with even resistance and latches without slamming? [Y/N] </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3123,42 +3123,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handle or frame fatigue fractures during lifting </t>
+          <t xml:space="preserve">Gasket retaining channel corroded; gasket dislodged from its seat </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher handles inspected for fatigue cracks? [Y/N] </t>
+          <t xml:space="preserve">Gasket is fully seated in its retaining channel at all points? [Y/N] </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3168,49 +3168,49 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.6 - Fatigue </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lifting webbing breaks under load due to UV degradation </t>
+          <t xml:space="preserve">Gasket adhesive failed due to thermal cycling; gasket detached from door </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher webbing inspected for fraying or UV damage? [Y/N] </t>
+          <t xml:space="preserve">Door gasket is fully adhered to the door surface with no peeling? [Y/N] </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3220,49 +3220,49 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webbing contaminated with fuel/oil causing degradation </t>
+          <t xml:space="preserve">Gasket contact surface on cabinet door edge corroded and pitted; seal compromised </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher fabric clean, free of contamination? [Y/N] </t>
+          <t xml:space="preserve">Gasket contact surfaces are smooth and free from pitting corrosion? [Y/N] </t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3279,42 +3279,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padding/foam degraded </t>
+          <t xml:space="preserve">Cabinet door edge dented where gasket seats; gap exists between gasket and metal </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher padding condition and thickness inspected? [Y/N] </t>
+          <t xml:space="preserve">The door sealing edge is straight and free from dents or deformation? [Y/N] </t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3331,42 +3331,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leg or footrest breaks during use </t>
+          <t xml:space="preserve">Gasket retaining strip (if fitted) broken; gasket can be pushed out </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher legs secure and free of damage? [Y/N] </t>
+          <t xml:space="preserve">The gasket retaining strip is intact and holding the gasket securely? [Y/N] </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3383,42 +3383,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Stretcher Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide safe transport of injured persons away from danger zone </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">5.2 - Contamination </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wheel (if fitted) loose or detached </t>
+          <t xml:space="preserve">Gasket contaminated with dirt or salt; cannot seal properly </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stretcher wheels (if fitted) securely attached? [Y/N] </t>
+          <t xml:space="preserve">Gasket surfaces are clean and free from debris build-up? [Y/N] </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3435,42 +3435,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kit contents contaminated by moisture/dirt </t>
+          <t xml:space="preserve">Gasket retaining channel corroded; gasket partially dislodged </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">First aid kit contents and packaging clean and intact? [Y/N] </t>
+          <t xml:space="preserve">The gasket retaining channel is free of corrosion and deformation? [Y/N] </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3487,42 +3487,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">6.3 - Other </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Container latch or closure broken </t>
+          <t xml:space="preserve">Gasket partially comes out of channel when door is opened; needs re-seating </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">First aid kit closure functional? [Y/N]; Contents secured? [Y/N] </t>
+          <t xml:space="preserve">Gasket remains fully seated in its channel when the door is opened? [Y/N] </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">2.4 - Wear </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contents depleted or expired </t>
+          <t xml:space="preserve">Gasket has localized compression set; permanently flattened, no longer seals </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">First aid kit inventory complete and within expiration dates? [Y/N] </t>
+          <t xml:space="preserve">Gasket has uniform profile with no flat spots or compression set? [Y/N] </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3584,49 +3584,49 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">5.2 - Contamination </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kit contents not configured for helideck requirements </t>
+          <t xml:space="preserve">Cabinet drain valve (if fitted) stuck open due to debris; cannot seal against water ingress </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">First aid kit contents verified against helideck checklist? [Y/N] </t>
+          <t xml:space="preserve">Cabinet drain valve (if fitted) opens under water pressure and closes freely? [Y/N] </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3636,49 +3636,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Cabinetry Seals/Gasket Failure *</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Prevent ingress of water, dust, and salt spray into the storage cabinet </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kit packaging pouches torn </t>
+          <t xml:space="preserve">Cabinet drain pipe (if fitted) blocked by corrosion products; water trapped in cabinet </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">First aid kit packaging and pouches intact? [Y/N] </t>
+          <t xml:space="preserve">Cabinet drain line is clear and free from obstruction? [Y/N] </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3695,42 +3695,42 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metal container corroded </t>
+          <t xml:space="preserve">Axe handle split or broken; tool unusable </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">First aid kit container free of corrosion? [Y/N] </t>
+          <t xml:space="preserve">Rescue axe handle is intact with no splits, cracks, or splinters? [Y/N] </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3747,42 +3747,42 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kit box crushed </t>
+          <t xml:space="preserve">Crowbar severely corroded; reduced cross-section, structural integrity compromised </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">First aid kit container free of deformation? [Y/N] </t>
+          <t xml:space="preserve">Crowbar is free from deep pitting corrosion and is structurally sound? [Y/N] </t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3792,49 +3792,49 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.6 - Fatigue </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mounting bracket loose </t>
+          <t xml:space="preserve">Fatigue crack at junction of axe head and handle; head may detach </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">First aid kit securely stored in designated location? [Y/N] </t>
+          <t xml:space="preserve">Axe head is tightly secured to the handle with no lateral play? [Y/N] </t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3844,49 +3844,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>First Aid Kit Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediate first aid materials to treat injured persons </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">1.5 - Looseness </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kit box deformed, cannot close </t>
+          <t xml:space="preserve">Axe head wedge loose; head moves on the handle </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kit box free of deformation affecting closure? [Y/N] </t>
+          <t xml:space="preserve">The wedge securing the axe head is intact and properly seated? [Y/N] </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3903,42 +3903,42 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2 No signal/indication/alarm </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure gauge not working </t>
+          <t xml:space="preserve">Crowbar tip chipped or broken; cannot be used for prying </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA pressure gauge functioning and reading correctly? [Y/N] </t>
+          <t xml:space="preserve">Crowbar working tip and chisel edge are intact? [Y/N] </t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3948,49 +3948,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demand valve stuck closed </t>
+          <t xml:space="preserve">Crowbar shaft bent; cannot be used effectively for prying </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA demand valve operates and seals properly? [Y/N] </t>
+          <t xml:space="preserve">Crowbar shaft is straight and has no bends or deformation? [Y/N] </t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4000,49 +4000,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder valve or air passage partially blocked </t>
+          <t xml:space="preserve">Axe cutting edge heavily corroded; blade edge not sharp enough to cut </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA cylinder valve fully open and air path clear? [Y/N] </t>
+          <t xml:space="preserve">Axe cutting edge is free from corrosion and shows a visible sharpened profile? [Y/N] </t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4059,42 +4059,42 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">2.6 - Fatigue </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure regulator set incorrectly </t>
+          <t xml:space="preserve">Fatigue crack in crowbar shaft; bar may break under load </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA pressure regulator settings within specification? [Y/N] </t>
+          <t xml:space="preserve">Crowbar shaft is free of cracks detectable by visual inspection? [Y/N] </t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4111,42 +4111,42 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 - Contamination </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connection/valve corroded </t>
+          <t xml:space="preserve">Tools oily or greasy; slippery to handle during emergency </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA connection free of corrosion affecting seal? [Y/N] </t>
+          <t xml:space="preserve">Rescue tools are clean and free from oil, grease, or other contaminants? [Y/N] </t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4163,42 +4163,42 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">5.3 - Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">O-rings/seals worn </t>
+          <t xml:space="preserve">Rubber hand grip (if fitted) deteriorated or missing; poor user grip </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA seals and O-rings condition acceptable? [Y/N] </t>
+          <t xml:space="preserve">Hand grips on tools are present and free from cuts, tears, or deterioration? [Y/N] </t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4215,42 +4215,42 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder dented/deformed </t>
+          <t xml:space="preserve">Surface rust on axe head; cosmetic degradation </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA cylinder inspected for dents or deformation? [Y/N] </t>
+          <t xml:space="preserve">Axe head surface is free from active rust or corrosion? [Y/N] </t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4260,49 +4260,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.4 - Wear </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder surface corrosion could compromise containment </t>
+          <t xml:space="preserve">Axe cutting edge dull from use or corrosion; needs sharpening </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA cylinder external condition free of deep pitting? [Y/N] </t>
+          <t xml:space="preserve">Axe cutting edge is sharp and free from nicks or damage? [Y/N] </t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4312,49 +4312,49 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">1.6 - Sticking </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure gauge calibration drifted </t>
+          <t xml:space="preserve">Axe or crowbar jammed in storage bracket; cannot be removed quickly </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA pressure gauge calibration verified? [Y/N] </t>
+          <t xml:space="preserve">Each rescue tool can be easily removed from its storage bracket by hand? [Y/N] </t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4364,49 +4364,49 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 Faulty power/voltage </t>
+          <t xml:space="preserve">2.2 - Corrosion </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electronic alarm (if fitted) low battery </t>
+          <t xml:space="preserve">Storage bracket corroded and swollen; tool wedged in place </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA low pressure alarm functional? [Y/N] </t>
+          <t xml:space="preserve">Tool storage brackets are free from corrosion and hold tools without binding? [Y/N] </t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4416,49 +4416,49 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.4 - Deformation </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expiratory valve contaminated </t>
+          <t xml:space="preserve">Storage bracket bent; tool does not fit properly </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA expiratory valve clean and functioning? [Y/N] </t>
+          <t xml:space="preserve">Tool storage brackets are not bent or deformed and hold tools correctly? [Y/N] </t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4475,42 +4475,42 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Emergency Breathing Apparatus Failure *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide breathing protection for rescue personnel entering toxic atmosphere </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation (*) </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">6.3 - Other </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facemask frame cracked </t>
+          <t xml:space="preserve">Wrong tool stored in bracket; axe missing, crowbar duplicated </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">EBA facemask condition checked for cracks? [Y/N] </t>
+          <t xml:space="preserve">The correct tool is present in each designated bracket? [Y/N] </t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4520,49 +4520,49 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
+          <t>Rescue Axe / Crowbar Failure *</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
+          <t xml:space="preserve">Provide manual forcible entry capability for helicopter rescue operations </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation (*) </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">3.4 - Out of adjustment </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carabiner cracked under load – catastrophic failure </t>
+          <t xml:space="preserve">Tool bracket adjusted for wrong tool size; tool does not fit securely </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rescue carabiner inspected for cracks or damage? [Y/N] </t>
+          <t xml:space="preserve">Tool fits snugly in its bracket without rattling? [Y/N] </t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4579,42 +4579,42 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
+          <t>Rescue Stretcher Failure *</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
+          <t xml:space="preserve">Provide a rigid litter for casualty immobilization and transport from the helideck </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.5 - Breakage </t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on metal reduces load capacity </t>
+          <t xml:space="preserve">Stretcher frame cracked or fractured; cannot support a casualty </t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carabiner free of corrosion? [Y/N] </t>
+          <t xml:space="preserve">Stretcher frame and crossbars are free from cracks, fractures, or deformation? [Y/N] </t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4631,42 +4631,42 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
+          <t xml:space="preserve">LSHE - Helideck Safety Equipment </t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
+          <t xml:space="preserve">Provide immediate access to portable crash rescue equipment following a helicopter incident on the helideck </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
+          <t>Rescue Stretcher Failure *</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
+          <t xml:space="preserve">Provide a rigid litter for casualty immobilization and transport from the helideck </t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">BRD - Breakdown </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">2.4 - Wear </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gate jammed cannot open or close </t>
+          <t xml:space="preserve">Carrying handles or straps worn through; could fail during use </t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carabiner gate moves freely and self-latches? [Y/N] </t>
+          <t xml:space="preserve">Carrying handles/straps are intact with no cuts, fraying, or material degradation? [Y/N] </t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4674,731 +4674,7 @@
           <t xml:space="preserve">TBD </t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5 Looseness </t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gate hinge pin loose – risk of gate opening under load </t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carabiner hinge pin tight and secure? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gate hinge fatigue failure during use </t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carabiner inspected for wear and fatigue at hinge pivot? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.4 Wear </t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wear at gate locking mechanism reduces self-closing </t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carabiner locking mechanism condition checked? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.4 Wear </t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rough gate surface from wear </t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carabiner surface finish for smooth operation inspected? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation </t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gate deformed from overload </t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carabiner gate free of deformation? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise </t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5 Looseness </t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loose gate hinge makes rattling noise </t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carabiner hinge pin tightness checked? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Rescue Hook and Carabiner Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure attachment point for rescue lines and connectors </t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise </t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.4 Wear </t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Worn hinge pin causes squeaking </t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carabiner hinge pin condition inspected? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Rescue Rope / Lifeline Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure line for lowering/raising persons during rescue </t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.5 Breakage </t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rope breaks under load due to abrasion or UV degradation </t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rescue rope condition and safe working load verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Rescue Rope / Lifeline Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure line for lowering/raising persons during rescue </t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rope fibers fatigued from repeated loading </t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rescue rope service life and usage history reviewed? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Rescue Rope / Lifeline Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure line for lowering/raising persons during rescue </t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.4 Wear </t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rope surface wear reduces breaking strength </t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rescue rope inspected for surface wear or flat spots? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Rescue Rope / Lifeline Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure line for lowering/raising persons during rescue </t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2 Contamination </t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rope contaminated with oil/grease/chemicals </t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rescue rope free of chemical/oil contamination? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Rescue Rope / Lifeline Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure line for lowering/raising persons during rescue </t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Metal eye or thimble corroded weakens connection </t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rescue rope thimble/eye condition inspected? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Rescue Rope / Lifeline Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure line for lowering/raising persons during rescue </t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation </t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thimble deformed from overload </t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rescue rope thimble free of deformation? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helideck Safety Equipment </t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide immediately accessible portable crash rescue equipment and storage for emergency response after a helicopter incident </t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Rescue Rope / Lifeline Failure (*) *</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide secure line for lowering/raising persons during rescue </t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rope knots/kinks stuck, cannot run through pulley </t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Rescue rope free of knots/kinks</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
